--- a/Deterministic/Model Files/Segment Test/data_generation_codes/data/production_capacity_scenarios_NEW_20JUN.xlsx
+++ b/Deterministic/Model Files/Segment Test/data_generation_codes/data/production_capacity_scenarios_NEW_20JUN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model Files/L-Shaped/data_generation_codes/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data_generation_codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA9B0739-16C6-408D-900C-1C358A4FE259}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DD4851D-3CDB-4695-B793-D34671302AE4}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-2565" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -164,10 +164,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,13 +451,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,7 +492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -531,7 +527,7 @@
         <v>12100000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -566,7 +562,7 @@
         <v>55800000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -601,7 +597,7 @@
         <v>5460000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -636,7 +632,7 @@
         <v>18900000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -671,7 +667,7 @@
         <v>677000000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -706,7 +702,7 @@
         <v>1320000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -741,7 +737,7 @@
         <v>380000000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -776,7 +772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -811,7 +807,7 @@
         <v>89200000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -846,7 +842,7 @@
         <v>31900000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -881,7 +877,7 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -916,7 +912,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -951,7 +947,7 @@
         <v>42800000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -986,7 +982,7 @@
         <v>102000000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1021,647 +1017,17 @@
         <v>581000000</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="2">
-        <f>B2*0.7</f>
-        <v>5201000</v>
-      </c>
-      <c r="C19" s="2">
-        <f t="shared" ref="C19:K19" si="0">C2*0.7</f>
-        <v>7140000</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="0"/>
-        <v>8329999.9999999991</v>
-      </c>
-      <c r="E19" s="2">
-        <f t="shared" si="0"/>
-        <v>8329999.9999999991</v>
-      </c>
-      <c r="F19" s="2">
-        <f t="shared" si="0"/>
-        <v>8259999.9999999991</v>
-      </c>
-      <c r="G19" s="2">
-        <f t="shared" si="0"/>
-        <v>8189999.9999999991</v>
-      </c>
-      <c r="H19" s="2">
-        <f t="shared" si="0"/>
-        <v>8329999.9999999991</v>
-      </c>
-      <c r="I19" s="2">
-        <f t="shared" si="0"/>
-        <v>8189999.9999999991</v>
-      </c>
-      <c r="J19" s="2">
-        <f t="shared" si="0"/>
-        <v>8329999.9999999991</v>
-      </c>
-      <c r="K19" s="2">
-        <f t="shared" si="0"/>
-        <v>8470000</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
-        <f t="shared" ref="B20:K20" si="1">B3*0.7</f>
-        <v>36400000</v>
-      </c>
-      <c r="C20" s="2">
-        <f t="shared" si="1"/>
-        <v>40460000</v>
-      </c>
-      <c r="D20" s="2">
-        <f t="shared" si="1"/>
-        <v>40740000</v>
-      </c>
-      <c r="E20" s="2">
-        <f t="shared" si="1"/>
-        <v>38500000</v>
-      </c>
-      <c r="F20" s="2">
-        <f t="shared" si="1"/>
-        <v>38360000</v>
-      </c>
-      <c r="G20" s="2">
-        <f t="shared" si="1"/>
-        <v>38150000</v>
-      </c>
-      <c r="H20" s="2">
-        <f t="shared" si="1"/>
-        <v>38430000</v>
-      </c>
-      <c r="I20" s="2">
-        <f t="shared" si="1"/>
-        <v>38150000</v>
-      </c>
-      <c r="J20" s="2">
-        <f t="shared" si="1"/>
-        <v>38640000</v>
-      </c>
-      <c r="K20" s="2">
-        <f t="shared" si="1"/>
-        <v>39060000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="2">
-        <f t="shared" ref="B21:K21" si="2">B4*0.7</f>
-        <v>53270000</v>
-      </c>
-      <c r="C21" s="2">
-        <f t="shared" si="2"/>
-        <v>58939999.999999993</v>
-      </c>
-      <c r="D21" s="2">
-        <f t="shared" si="2"/>
-        <v>59989999.999999993</v>
-      </c>
-      <c r="E21" s="2">
-        <f t="shared" si="2"/>
-        <v>58100000</v>
-      </c>
-      <c r="F21" s="2">
-        <f t="shared" si="2"/>
-        <v>58450000</v>
-      </c>
-      <c r="G21" s="2">
-        <f t="shared" si="2"/>
-        <v>56490000</v>
-      </c>
-      <c r="H21" s="2">
-        <f t="shared" si="2"/>
-        <v>3779999.9999999995</v>
-      </c>
-      <c r="I21" s="2">
-        <f t="shared" si="2"/>
-        <v>3737999.9999999995</v>
-      </c>
-      <c r="J21" s="2">
-        <f t="shared" si="2"/>
-        <v>3779999.9999999995</v>
-      </c>
-      <c r="K21" s="2">
-        <f t="shared" si="2"/>
-        <v>3821999.9999999995</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="2">
-        <f t="shared" ref="B22:K22" si="3">B5*0.7</f>
-        <v>8119999.9999999991</v>
-      </c>
-      <c r="C22" s="2">
-        <f t="shared" si="3"/>
-        <v>11130000</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="3"/>
-        <v>13020000</v>
-      </c>
-      <c r="E22" s="2">
-        <f t="shared" si="3"/>
-        <v>12950000</v>
-      </c>
-      <c r="F22" s="2">
-        <f t="shared" si="3"/>
-        <v>12950000</v>
-      </c>
-      <c r="G22" s="2">
-        <f t="shared" si="3"/>
-        <v>12740000</v>
-      </c>
-      <c r="H22" s="2">
-        <f t="shared" si="3"/>
-        <v>13020000</v>
-      </c>
-      <c r="I22" s="2">
-        <f t="shared" si="3"/>
-        <v>12810000</v>
-      </c>
-      <c r="J22" s="2">
-        <f t="shared" si="3"/>
-        <v>13020000</v>
-      </c>
-      <c r="K22" s="2">
-        <f t="shared" si="3"/>
-        <v>13230000</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="2">
-        <f t="shared" ref="B23:K23" si="4">B6*0.7</f>
-        <v>116900000</v>
-      </c>
-      <c r="C23" s="2">
-        <f t="shared" si="4"/>
-        <v>130199999.99999999</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="4"/>
-        <v>131599999.99999999</v>
-      </c>
-      <c r="E23" s="2">
-        <f t="shared" si="4"/>
-        <v>125299999.99999999</v>
-      </c>
-      <c r="F23" s="2">
-        <f t="shared" si="4"/>
-        <v>123899999.99999999</v>
-      </c>
-      <c r="G23" s="2">
-        <f t="shared" si="4"/>
-        <v>121099999.99999999</v>
-      </c>
-      <c r="H23" s="2">
-        <f t="shared" si="4"/>
-        <v>472499999.99999994</v>
-      </c>
-      <c r="I23" s="2">
-        <f t="shared" si="4"/>
-        <v>470399999.99999994</v>
-      </c>
-      <c r="J23" s="2">
-        <f t="shared" si="4"/>
-        <v>472499999.99999994</v>
-      </c>
-      <c r="K23" s="2">
-        <f t="shared" si="4"/>
-        <v>473899999.99999994</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="2">
-        <f t="shared" ref="B24:K24" si="5">B7*0.7</f>
-        <v>9730000</v>
-      </c>
-      <c r="C24" s="2">
-        <f t="shared" si="5"/>
-        <v>10640000</v>
-      </c>
-      <c r="D24" s="2">
-        <f t="shared" si="5"/>
-        <v>11060000</v>
-      </c>
-      <c r="E24" s="2">
-        <f t="shared" si="5"/>
-        <v>11900000</v>
-      </c>
-      <c r="F24" s="2">
-        <f t="shared" si="5"/>
-        <v>12390000</v>
-      </c>
-      <c r="G24" s="2">
-        <f t="shared" si="5"/>
-        <v>11270000</v>
-      </c>
-      <c r="H24" s="2">
-        <f t="shared" si="5"/>
-        <v>1113000</v>
-      </c>
-      <c r="I24" s="2">
-        <f t="shared" si="5"/>
-        <v>1113000</v>
-      </c>
-      <c r="J24" s="2">
-        <f t="shared" si="5"/>
-        <v>889000</v>
-      </c>
-      <c r="K24" s="2">
-        <f t="shared" si="5"/>
-        <v>923999.99999999988</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="2">
-        <f t="shared" ref="B25:K25" si="6">B8*0.7</f>
-        <v>224700000</v>
-      </c>
-      <c r="C25" s="2">
-        <f t="shared" si="6"/>
-        <v>235899999.99999997</v>
-      </c>
-      <c r="D25" s="2">
-        <f t="shared" si="6"/>
-        <v>258299999.99999997</v>
-      </c>
-      <c r="E25" s="2">
-        <f t="shared" si="6"/>
-        <v>261799999.99999997</v>
-      </c>
-      <c r="F25" s="2">
-        <f t="shared" si="6"/>
-        <v>277900000</v>
-      </c>
-      <c r="G25" s="2">
-        <f t="shared" si="6"/>
-        <v>299600000</v>
-      </c>
-      <c r="H25" s="2">
-        <f t="shared" si="6"/>
-        <v>251299999.99999997</v>
-      </c>
-      <c r="I25" s="2">
-        <f t="shared" si="6"/>
-        <v>275100000</v>
-      </c>
-      <c r="J25" s="2">
-        <f t="shared" si="6"/>
-        <v>257599999.99999997</v>
-      </c>
-      <c r="K25" s="2">
-        <f t="shared" si="6"/>
-        <v>265999999.99999997</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="2">
-        <f t="shared" ref="B26:K26" si="7">B9*0.7</f>
-        <v>71400000</v>
-      </c>
-      <c r="C26" s="2">
-        <f t="shared" si="7"/>
-        <v>78400000</v>
-      </c>
-      <c r="D26" s="2">
-        <f t="shared" si="7"/>
-        <v>79800000</v>
-      </c>
-      <c r="E26" s="2">
-        <f t="shared" si="7"/>
-        <v>77000000</v>
-      </c>
-      <c r="F26" s="2">
-        <f t="shared" si="7"/>
-        <v>77000000</v>
-      </c>
-      <c r="G26" s="2">
-        <f t="shared" si="7"/>
-        <v>74200000</v>
-      </c>
-      <c r="H26" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
-        <f t="shared" ref="B27:K27" si="8">B10*0.7</f>
-        <v>55510000</v>
-      </c>
-      <c r="C27" s="2">
-        <f t="shared" si="8"/>
-        <v>63349999.999999993</v>
-      </c>
-      <c r="D27" s="2">
-        <f t="shared" si="8"/>
-        <v>65799999.999999993</v>
-      </c>
-      <c r="E27" s="2">
-        <f t="shared" si="8"/>
-        <v>62649999.999999993</v>
-      </c>
-      <c r="F27" s="2">
-        <f t="shared" si="8"/>
-        <v>62369999.999999993</v>
-      </c>
-      <c r="G27" s="2">
-        <f t="shared" si="8"/>
-        <v>61179999.999999993</v>
-      </c>
-      <c r="H27" s="2">
-        <f t="shared" si="8"/>
-        <v>61949999.999999993</v>
-      </c>
-      <c r="I27" s="2">
-        <f t="shared" si="8"/>
-        <v>61039999.999999993</v>
-      </c>
-      <c r="J27" s="2">
-        <f t="shared" si="8"/>
-        <v>61809999.999999993</v>
-      </c>
-      <c r="K27" s="2">
-        <f t="shared" si="8"/>
-        <v>62439999.999999993</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="2">
-        <f t="shared" ref="B28:K28" si="9">B11*0.7</f>
-        <v>11830000</v>
-      </c>
-      <c r="C28" s="2">
-        <f t="shared" si="9"/>
-        <v>11970000</v>
-      </c>
-      <c r="D28" s="2">
-        <f t="shared" si="9"/>
-        <v>17500000</v>
-      </c>
-      <c r="E28" s="2">
-        <f t="shared" si="9"/>
-        <v>46480000</v>
-      </c>
-      <c r="F28" s="2">
-        <f t="shared" si="9"/>
-        <v>59149999.999999993</v>
-      </c>
-      <c r="G28" s="2">
-        <f t="shared" si="9"/>
-        <v>41300000</v>
-      </c>
-      <c r="H28" s="2">
-        <f t="shared" si="9"/>
-        <v>26950000</v>
-      </c>
-      <c r="I28" s="2">
-        <f t="shared" si="9"/>
-        <v>27020000</v>
-      </c>
-      <c r="J28" s="2">
-        <f t="shared" si="9"/>
-        <v>21490000</v>
-      </c>
-      <c r="K28" s="2">
-        <f t="shared" si="9"/>
-        <v>22330000</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="2">
-        <f t="shared" ref="B29:K29" si="10">B12*0.7</f>
-        <v>9800000</v>
-      </c>
-      <c r="C29" s="2">
-        <f t="shared" si="10"/>
-        <v>10920000</v>
-      </c>
-      <c r="D29" s="2">
-        <f t="shared" si="10"/>
-        <v>11130000</v>
-      </c>
-      <c r="E29" s="2">
-        <f t="shared" si="10"/>
-        <v>10640000</v>
-      </c>
-      <c r="F29" s="2">
-        <f t="shared" si="10"/>
-        <v>10640000</v>
-      </c>
-      <c r="G29" s="2">
-        <f t="shared" si="10"/>
-        <v>10430000</v>
-      </c>
-      <c r="H29" s="2">
-        <f t="shared" si="10"/>
-        <v>9660000</v>
-      </c>
-      <c r="I29" s="2">
-        <f t="shared" si="10"/>
-        <v>9590000</v>
-      </c>
-      <c r="J29" s="2">
-        <f t="shared" si="10"/>
-        <v>9730000</v>
-      </c>
-      <c r="K29" s="2">
-        <f t="shared" si="10"/>
-        <v>9800000</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="2">
-        <f t="shared" ref="B30:K30" si="11">B13*0.7</f>
-        <v>63419999.999999993</v>
-      </c>
-      <c r="C30" s="2">
-        <f t="shared" si="11"/>
-        <v>75600000</v>
-      </c>
-      <c r="D30" s="2">
-        <f t="shared" si="11"/>
-        <v>84700000</v>
-      </c>
-      <c r="E30" s="2">
-        <f t="shared" si="11"/>
-        <v>83300000</v>
-      </c>
-      <c r="F30" s="2">
-        <f t="shared" si="11"/>
-        <v>89600000</v>
-      </c>
-      <c r="G30" s="2">
-        <f t="shared" si="11"/>
-        <v>88900000</v>
-      </c>
-      <c r="H30" s="2">
-        <f t="shared" si="11"/>
-        <v>90300000</v>
-      </c>
-      <c r="I30" s="2">
-        <f t="shared" si="11"/>
-        <v>88200000</v>
-      </c>
-      <c r="J30" s="2">
-        <f t="shared" si="11"/>
-        <v>88900000</v>
-      </c>
-      <c r="K30" s="2">
-        <f t="shared" si="11"/>
-        <v>88900000</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="2">
-        <f t="shared" ref="B31:K31" si="12">B14*0.7</f>
-        <v>43540000</v>
-      </c>
-      <c r="C31" s="2">
-        <f t="shared" si="12"/>
-        <v>52360000</v>
-      </c>
-      <c r="D31" s="2">
-        <f t="shared" si="12"/>
-        <v>51170000</v>
-      </c>
-      <c r="E31" s="2">
-        <f t="shared" si="12"/>
-        <v>46830000</v>
-      </c>
-      <c r="F31" s="2">
-        <f t="shared" si="12"/>
-        <v>48860000</v>
-      </c>
-      <c r="G31" s="2">
-        <f t="shared" si="12"/>
-        <v>41090000</v>
-      </c>
-      <c r="H31" s="2">
-        <f t="shared" si="12"/>
-        <v>30799999.999999996</v>
-      </c>
-      <c r="I31" s="2">
-        <f t="shared" si="12"/>
-        <v>29260000</v>
-      </c>
-      <c r="J31" s="2">
-        <f t="shared" si="12"/>
-        <v>29679999.999999996</v>
-      </c>
-      <c r="K31" s="2">
-        <f t="shared" si="12"/>
-        <v>29959999.999999996</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="2">
-        <f t="shared" ref="B32:K32" si="13">B15*0.7</f>
-        <v>63349999.999999993</v>
-      </c>
-      <c r="C32" s="2">
-        <f t="shared" si="13"/>
-        <v>81900000</v>
-      </c>
-      <c r="D32" s="2">
-        <f t="shared" si="13"/>
-        <v>91700000</v>
-      </c>
-      <c r="E32" s="2">
-        <f t="shared" si="13"/>
-        <v>91000000</v>
-      </c>
-      <c r="F32" s="2">
-        <f t="shared" si="13"/>
-        <v>91000000</v>
-      </c>
-      <c r="G32" s="2">
-        <f t="shared" si="13"/>
-        <v>89600000</v>
-      </c>
-      <c r="H32" s="2">
-        <f t="shared" si="13"/>
-        <v>69930000</v>
-      </c>
-      <c r="I32" s="2">
-        <f t="shared" si="13"/>
-        <v>68810000</v>
-      </c>
-      <c r="J32" s="2">
-        <f t="shared" si="13"/>
-        <v>70000000</v>
-      </c>
-      <c r="K32" s="2">
-        <f t="shared" si="13"/>
-        <v>71400000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="2">
-        <f t="shared" ref="B33:K33" si="14">B16*0.7</f>
-        <v>557900000</v>
-      </c>
-      <c r="C33" s="2">
-        <f t="shared" si="14"/>
-        <v>572600000</v>
-      </c>
-      <c r="D33" s="2">
-        <f t="shared" si="14"/>
-        <v>597800000</v>
-      </c>
-      <c r="E33" s="2">
-        <f t="shared" si="14"/>
-        <v>553700000</v>
-      </c>
-      <c r="F33" s="2">
-        <f t="shared" si="14"/>
-        <v>571900000</v>
-      </c>
-      <c r="G33" s="2">
-        <f t="shared" si="14"/>
-        <v>572600000</v>
-      </c>
-      <c r="H33" s="2">
-        <f t="shared" si="14"/>
-        <v>377300000</v>
-      </c>
-      <c r="I33" s="2">
-        <f t="shared" si="14"/>
-        <v>434000000</v>
-      </c>
-      <c r="J33" s="2">
-        <f t="shared" si="14"/>
-        <v>385700000</v>
-      </c>
-      <c r="K33" s="2">
-        <f t="shared" si="14"/>
-        <v>406700000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:K16">
@@ -1683,9 +1049,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1720,7 +1086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1755,7 +1121,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1790,7 +1156,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1825,7 +1191,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1860,7 +1226,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1895,7 +1261,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1930,7 +1296,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1965,7 +1331,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2000,7 +1366,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2035,7 +1401,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2070,7 +1436,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2105,7 +1471,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2140,7 +1506,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2175,7 +1541,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2210,7 +1576,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2253,9 +1619,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2290,7 +1656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2325,7 +1691,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2360,7 +1726,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2395,7 +1761,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2430,7 +1796,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2465,7 +1831,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2500,7 +1866,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2535,7 +1901,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2570,7 +1936,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2605,7 +1971,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2640,7 +2006,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2675,7 +2041,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2710,7 +2076,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2745,7 +2111,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2780,7 +2146,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2823,9 +2189,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2860,7 +2226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2895,7 +2261,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2930,7 +2296,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2965,7 +2331,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3000,7 +2366,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3035,7 +2401,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3070,7 +2436,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3105,7 +2471,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3140,7 +2506,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3175,7 +2541,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3210,7 +2576,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3245,7 +2611,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3280,7 +2646,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3315,7 +2681,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3350,7 +2716,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3393,9 +2759,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3430,7 +2796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3465,7 +2831,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3500,7 +2866,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3535,7 +2901,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3570,7 +2936,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3605,7 +2971,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3640,7 +3006,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3675,7 +3041,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3710,7 +3076,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3745,7 +3111,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3780,7 +3146,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3815,7 +3181,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3850,7 +3216,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3885,7 +3251,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3920,7 +3286,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3963,9 +3329,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4000,7 +3366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4035,7 +3401,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4070,7 +3436,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4105,7 +3471,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4140,7 +3506,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4175,7 +3541,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4210,7 +3576,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4245,7 +3611,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4280,7 +3646,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4315,7 +3681,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4350,7 +3716,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4385,7 +3751,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4420,7 +3786,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4455,7 +3821,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4490,7 +3856,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -4533,13 +3899,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4574,7 +3940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4609,7 +3975,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4644,7 +4010,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4679,7 +4045,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4714,7 +4080,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4749,7 +4115,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4784,7 +4150,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4819,7 +4185,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4854,7 +4220,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4889,7 +4255,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4924,7 +4290,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4959,7 +4325,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4994,7 +4360,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -5029,7 +4395,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -5064,7 +4430,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
